--- a/fixtures/workbooks/synthetic_segmented_golden.xlsx
+++ b/fixtures/workbooks/synthetic_segmented_golden.xlsx
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Widget ID</t>
+          <t>Member ID</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Synthetic widget identifier</t>
+          <t>Synthetic member identifier</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>SYN_WIDGET_ID</t>
+          <t>SYN_MEMBER_ID</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Synthetic widget identifier</t>
+          <t>Synthetic member identifier</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>SYN_WIDGET_ID</t>
+          <t>SYN_MEMBER_ID</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Synthetic widget identifier</t>
+          <t>Synthetic member identifier</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Record Count</t>
+          <t>Record Type</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1699,12 +1699,13 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Number of Detail records in the file</t>
+          <t>Static text identifying the record as the trailer record.
+Contains the value ******</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Must equal the Detail row count</t>
+          <t>Load as is</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1724,7 +1725,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>SYN_REC_CNT</t>
+          <t>SYN_REC_TYPE</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -1734,7 +1735,8 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Number of Detail records in the file</t>
+          <t>Static text identifying the record as the trailer record.
+Contains the value ******</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -1759,7 +1761,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>SYN_REC_CNT</t>
+          <t>SYN_REC_TYPE</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -1769,7 +1771,8 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Number of Detail records in the file</t>
+          <t>Static text identifying the record as the trailer record.
+Contains the value ******</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -1789,7 +1792,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>File Sequence</t>
+          <t>Record Count</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1809,12 +1812,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sequence number within the set</t>
+          <t>Number of Detail records in the file</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Load as is</t>
+          <t>Must equal the Detail row count</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1834,7 +1837,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>SYN_FILE_SEQ</t>
+          <t>SYN_REC_CNT</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -1844,7 +1847,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Sequence number within the set</t>
+          <t>Number of Detail records in the file</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -1869,7 +1872,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>SYN_FILE_SEQ</t>
+          <t>SYN_REC_CNT</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -1879,7 +1882,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Sequence number within the set</t>
+          <t>Number of Detail records in the file</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
